--- a/output/full_scan/batch_seq1_2026-09-09.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-09.xlsx
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>205.9101623771402</v>
+        <v>205.9101623771401</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>6.57</v>
